--- a/probe_contours.xlsx
+++ b/probe_contours.xlsx
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,7 +823,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>-22</v>
@@ -831,7 +831,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="B7" t="n">
         <v>34</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B8" t="n">
         <v>295</v>
@@ -847,7 +847,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B9" t="n">
         <v>425</v>
@@ -855,9 +855,225 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B10" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>213</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>213</v>
+      </c>
+      <c r="B12" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>236</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>282</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>328</v>
+      </c>
+      <c r="B16" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>328</v>
+      </c>
+      <c r="B17" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>328</v>
+      </c>
+      <c r="B18" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>328</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>463</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>463</v>
+      </c>
+      <c r="B21" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>463</v>
+      </c>
+      <c r="B22" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>486</v>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>532</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>578</v>
+      </c>
+      <c r="B25" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>578</v>
+      </c>
+      <c r="B26" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>578</v>
+      </c>
+      <c r="B27" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>578</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>713</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>713</v>
+      </c>
+      <c r="B30" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>713</v>
+      </c>
+      <c r="B31" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>736</v>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>782</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>828</v>
+      </c>
+      <c r="B34" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>828</v>
+      </c>
+      <c r="B35" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>828</v>
+      </c>
+      <c r="B36" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>828</v>
+      </c>
+      <c r="B37" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -1860,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1901,7 +2117,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
         <v>-65</v>
@@ -1909,7 +2125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -1917,7 +2133,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B7" t="n">
         <v>825</v>
@@ -1925,9 +2141,65 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B8" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>210</v>
+      </c>
+      <c r="B10" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>220</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>265</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>310</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>310</v>
+      </c>
+      <c r="B14" t="n">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>310</v>
+      </c>
+      <c r="B15" t="n">
         <v>9000</v>
       </c>
     </row>
@@ -6257,7 +6529,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="B2" t="n">
         <v>6000</v>
@@ -6265,7 +6537,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="B3" t="n">
         <v>840</v>
@@ -6273,7 +6545,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="B4" t="n">
         <v>800</v>
@@ -6281,7 +6553,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-10</v>
+        <v>-36</v>
       </c>
       <c r="B5" t="n">
         <v>-10</v>
@@ -6289,7 +6561,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="B6" t="n">
         <v>-20</v>
@@ -6297,7 +6569,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
         <v>-10</v>
@@ -6313,7 +6585,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B9" t="n">
         <v>800</v>
@@ -6321,7 +6593,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="B10" t="n">
         <v>-10</v>
@@ -6329,7 +6601,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>150</v>
+        <v>144.5</v>
       </c>
       <c r="B11" t="n">
         <v>-20</v>
@@ -6337,7 +6609,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B12" t="n">
         <v>-10</v>
@@ -6353,7 +6625,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B14" t="n">
         <v>800</v>
@@ -6361,7 +6633,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B15" t="n">
         <v>-10</v>
@@ -6369,7 +6641,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300</v>
+        <v>294.5</v>
       </c>
       <c r="B16" t="n">
         <v>-20</v>
@@ -6377,7 +6649,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B17" t="n">
         <v>-10</v>
@@ -6393,7 +6665,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B19" t="n">
         <v>800</v>
@@ -6401,7 +6673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="B20" t="n">
         <v>-10</v>
@@ -6409,7 +6681,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>450</v>
+        <v>444.5</v>
       </c>
       <c r="B21" t="n">
         <v>-20</v>
@@ -6417,7 +6689,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="B22" t="n">
         <v>-10</v>
@@ -7847,15 +8119,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -7863,7 +8135,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>400</v>
@@ -7871,7 +8143,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>6000</v>
@@ -10446,7 +10718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10495,15 +10767,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -10511,7 +10783,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>400</v>
@@ -10519,10 +10791,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -10530,20 +10802,20 @@
         <v>140</v>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -10551,41 +10823,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B13" t="n">
-        <v>-50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>182</v>
-      </c>
-      <c r="B16" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>182</v>
-      </c>
-      <c r="B17" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -14434,7 +14690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14483,15 +14739,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -14499,7 +14755,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>400</v>
@@ -14507,10 +14763,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -14518,20 +14774,20 @@
         <v>140</v>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -14539,41 +14795,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B13" t="n">
-        <v>-50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>182</v>
-      </c>
-      <c r="B16" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>182</v>
-      </c>
-      <c r="B17" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -17656,7 +17896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17705,15 +17945,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -17721,7 +17961,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>400</v>
@@ -17729,10 +17969,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -17740,20 +17980,20 @@
         <v>140</v>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -17761,41 +18001,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B13" t="n">
-        <v>-50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>182</v>
-      </c>
-      <c r="B16" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>182</v>
-      </c>
-      <c r="B17" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -20601,15 +20825,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -20617,7 +20841,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>400</v>
@@ -20625,7 +20849,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>6000</v>
@@ -22588,7 +22812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22637,15 +22861,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -22653,7 +22877,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>400</v>
@@ -22661,10 +22885,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -22672,20 +22896,20 @@
         <v>140</v>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -22693,41 +22917,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B13" t="n">
-        <v>-50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>182</v>
-      </c>
-      <c r="B16" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>182</v>
-      </c>
-      <c r="B17" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -24627,15 +24835,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -24643,7 +24851,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>400</v>
@@ -24651,7 +24859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>6000</v>
@@ -26068,7 +26276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26117,15 +26325,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -26133,7 +26341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>400</v>
@@ -26141,10 +26349,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B9" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
@@ -26152,20 +26360,20 @@
         <v>140</v>
       </c>
       <c r="B10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -26173,41 +26381,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B13" t="n">
-        <v>-50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>182</v>
-      </c>
-      <c r="B16" t="n">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>182</v>
-      </c>
-      <c r="B17" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -28156,7 +28348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28205,7 +28397,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>-22</v>
@@ -28213,7 +28405,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="B7" t="n">
         <v>34</v>
@@ -28221,7 +28413,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B8" t="n">
         <v>295</v>
@@ -28229,7 +28421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B9" t="n">
         <v>425</v>
@@ -28237,9 +28429,225 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B10" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>213</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>213</v>
+      </c>
+      <c r="B12" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>236</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>282</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>328</v>
+      </c>
+      <c r="B16" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>328</v>
+      </c>
+      <c r="B17" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>328</v>
+      </c>
+      <c r="B18" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>328</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>463</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>463</v>
+      </c>
+      <c r="B21" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>463</v>
+      </c>
+      <c r="B22" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>486</v>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>532</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>578</v>
+      </c>
+      <c r="B25" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>578</v>
+      </c>
+      <c r="B26" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>578</v>
+      </c>
+      <c r="B27" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>578</v>
+      </c>
+      <c r="B28" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>713</v>
+      </c>
+      <c r="B29" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>713</v>
+      </c>
+      <c r="B30" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>713</v>
+      </c>
+      <c r="B31" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>736</v>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>782</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>828</v>
+      </c>
+      <c r="B34" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>828</v>
+      </c>
+      <c r="B35" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>828</v>
+      </c>
+      <c r="B36" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>828</v>
+      </c>
+      <c r="B37" t="n">
         <v>9000</v>
       </c>
     </row>

--- a/probe_contours.xlsx
+++ b/probe_contours.xlsx
@@ -5450,7 +5450,7 @@
         <v>-10</v>
       </c>
       <c r="B2" t="n">
-        <v>1260</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="3">
@@ -5482,7 +5482,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>1260</v>
+        <v>2580</v>
       </c>
     </row>
   </sheetData>

--- a/probe_contours.xlsx
+++ b/probe_contours.xlsx
@@ -778,7 +778,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -786,7 +786,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -794,7 +794,7 @@
         <v>77.5</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -818,7 +818,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -826,7 +826,7 @@
         <v>285</v>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -834,7 +834,7 @@
         <v>327.5</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -858,7 +858,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -866,7 +866,7 @@
         <v>535</v>
       </c>
       <c r="B15" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -874,7 +874,7 @@
         <v>577.5</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -898,7 +898,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -906,7 +906,7 @@
         <v>785</v>
       </c>
       <c r="B20" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +914,7 @@
         <v>827.5</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -980,7 +980,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -988,7 +988,7 @@
         <v>8.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -996,7 +996,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -1020,7 +1020,7 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -1028,7 +1028,7 @@
         <v>208.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -1036,7 +1036,7 @@
         <v>224.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -1060,7 +1060,7 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -1068,7 +1068,7 @@
         <v>408.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -1076,7 +1076,7 @@
         <v>424.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -1108,7 +1108,7 @@
         <v>608.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -1116,7 +1116,7 @@
         <v>624.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -1140,7 +1140,7 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
@@ -1148,7 +1148,7 @@
         <v>808.5</v>
       </c>
       <c r="B25" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -1156,7 +1156,7 @@
         <v>824.5</v>
       </c>
       <c r="B26" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -1180,7 +1180,7 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
@@ -1188,7 +1188,7 @@
         <v>1008.5</v>
       </c>
       <c r="B30" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -1196,7 +1196,7 @@
         <v>1024.5</v>
       </c>
       <c r="B31" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -1262,7 +1262,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1270,7 +1270,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -1278,7 +1278,7 @@
         <v>45.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -1302,7 +1302,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -1310,7 +1310,7 @@
         <v>169</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -1318,7 +1318,7 @@
         <v>195.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -1384,7 +1384,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -1400,7 +1400,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -1424,7 +1424,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -1432,7 +1432,7 @@
         <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -1440,7 +1440,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -1638,7 +1638,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1646,7 +1646,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -1654,7 +1654,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -1678,7 +1678,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -1686,7 +1686,7 @@
         <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -1760,7 +1760,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="5">
@@ -1768,7 +1768,7 @@
         <v>26</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="6">
@@ -1776,7 +1776,7 @@
         <v>59.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="7">
@@ -1800,7 +1800,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="10">
@@ -1808,7 +1808,7 @@
         <v>276</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="11">
@@ -1816,7 +1816,7 @@
         <v>309.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="12">
@@ -1882,15 +1882,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -1898,7 +1898,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -1922,15 +1922,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -1938,7 +1938,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -2318,7 +2318,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -2326,7 +2326,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -2334,7 +2334,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2358,7 +2358,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -2366,7 +2366,7 @@
         <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -2374,7 +2374,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -2398,7 +2398,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -2406,7 +2406,7 @@
         <v>511.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -2414,7 +2414,7 @@
         <v>530.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -2438,7 +2438,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -2446,7 +2446,7 @@
         <v>761.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -2454,7 +2454,7 @@
         <v>780.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -2520,7 +2520,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -2528,7 +2528,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -2536,7 +2536,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2560,7 +2560,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -2568,7 +2568,7 @@
         <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -2576,7 +2576,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -2600,7 +2600,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -2608,7 +2608,7 @@
         <v>511.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -2616,7 +2616,7 @@
         <v>530.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -2640,7 +2640,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -2648,7 +2648,7 @@
         <v>761.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-125</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -2656,7 +2656,7 @@
         <v>780.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -2722,7 +2722,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -2730,7 +2730,7 @@
         <v>2.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -2738,7 +2738,7 @@
         <v>12.5</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2762,7 +2762,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -2770,7 +2770,7 @@
         <v>252.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>262.5</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -2802,7 +2802,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -2810,7 +2810,7 @@
         <v>502.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -2818,7 +2818,7 @@
         <v>512.5</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -2842,7 +2842,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -2850,7 +2850,7 @@
         <v>752.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -2858,7 +2858,7 @@
         <v>762.5</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -2924,7 +2924,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -2932,7 +2932,7 @@
         <v>2.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -2940,7 +2940,7 @@
         <v>12.5</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2964,7 +2964,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -2972,7 +2972,7 @@
         <v>252.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -2980,7 +2980,7 @@
         <v>262.5</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -3004,7 +3004,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -3012,7 +3012,7 @@
         <v>502.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -3020,7 +3020,7 @@
         <v>512.5</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -3044,7 +3044,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -3052,7 +3052,7 @@
         <v>752.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -3060,7 +3060,7 @@
         <v>762.5</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -3126,7 +3126,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -3134,7 +3134,7 @@
         <v>8.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -3142,7 +3142,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -3166,7 +3166,7 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -3174,7 +3174,7 @@
         <v>208.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -3182,7 +3182,7 @@
         <v>224.5</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -3206,7 +3206,7 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -3214,7 +3214,7 @@
         <v>408.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -3222,7 +3222,7 @@
         <v>424.5</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -3246,7 +3246,7 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -3254,7 +3254,7 @@
         <v>608.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -3262,7 +3262,7 @@
         <v>624.5</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -3286,7 +3286,7 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
@@ -3294,7 +3294,7 @@
         <v>808.5</v>
       </c>
       <c r="B25" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -3302,7 +3302,7 @@
         <v>824.5</v>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -3326,7 +3326,7 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
@@ -3334,7 +3334,7 @@
         <v>1008.5</v>
       </c>
       <c r="B30" t="n">
-        <v>-24</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -3342,7 +3342,7 @@
         <v>1024.5</v>
       </c>
       <c r="B31" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -3408,7 +3408,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -3416,7 +3416,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -3424,7 +3424,7 @@
         <v>45.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -3448,7 +3448,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -3456,7 +3456,7 @@
         <v>169</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -3464,7 +3464,7 @@
         <v>195.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -3530,7 +3530,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="5">
@@ -3538,7 +3538,7 @@
         <v>26</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="6">
@@ -3546,7 +3546,7 @@
         <v>59.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="7">
@@ -3570,7 +3570,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="10">
@@ -3578,7 +3578,7 @@
         <v>276</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="11">
@@ -3586,7 +3586,7 @@
         <v>309.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="12">
@@ -3718,7 +3718,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -3726,7 +3726,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -3734,7 +3734,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -3758,7 +3758,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -3766,7 +3766,7 @@
         <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -3774,7 +3774,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -3798,7 +3798,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -3806,7 +3806,7 @@
         <v>511.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -3814,7 +3814,7 @@
         <v>530.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -3838,7 +3838,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -3846,7 +3846,7 @@
         <v>761.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -3854,7 +3854,7 @@
         <v>780.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -3920,7 +3920,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -3928,7 +3928,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -3936,7 +3936,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -3960,7 +3960,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -3968,7 +3968,7 @@
         <v>261.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -3976,7 +3976,7 @@
         <v>280.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -4000,7 +4000,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -4008,7 +4008,7 @@
         <v>511.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -4016,7 +4016,7 @@
         <v>530.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -4040,7 +4040,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4048,7 +4048,7 @@
         <v>761.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-100</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -4056,7 +4056,7 @@
         <v>780.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -4122,7 +4122,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -4130,7 +4130,7 @@
         <v>8.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -4138,7 +4138,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -4162,7 +4162,7 @@
         <v>117.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -4170,7 +4170,7 @@
         <v>133.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -4178,7 +4178,7 @@
         <v>149.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -4202,7 +4202,7 @@
         <v>242.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -4210,7 +4210,7 @@
         <v>258.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -4218,7 +4218,7 @@
         <v>274.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -4242,7 +4242,7 @@
         <v>367.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4250,7 +4250,7 @@
         <v>383.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -4258,7 +4258,7 @@
         <v>399.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -4282,7 +4282,7 @@
         <v>492.5</v>
       </c>
       <c r="B24" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
@@ -4290,7 +4290,7 @@
         <v>508.5</v>
       </c>
       <c r="B25" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -4298,7 +4298,7 @@
         <v>524.5</v>
       </c>
       <c r="B26" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -4322,7 +4322,7 @@
         <v>617.5</v>
       </c>
       <c r="B29" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
@@ -4330,7 +4330,7 @@
         <v>633.5</v>
       </c>
       <c r="B30" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -4338,7 +4338,7 @@
         <v>649.5</v>
       </c>
       <c r="B31" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -4362,7 +4362,7 @@
         <v>742.5</v>
       </c>
       <c r="B34" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="35">
@@ -4370,7 +4370,7 @@
         <v>758.5</v>
       </c>
       <c r="B35" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="36">
@@ -4378,7 +4378,7 @@
         <v>774.5</v>
       </c>
       <c r="B36" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="37">
@@ -4402,7 +4402,7 @@
         <v>867.5</v>
       </c>
       <c r="B39" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="40">
@@ -4410,7 +4410,7 @@
         <v>883.5</v>
       </c>
       <c r="B40" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="41">
@@ -4418,7 +4418,7 @@
         <v>899.5</v>
       </c>
       <c r="B41" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="42">
@@ -4484,7 +4484,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -4492,7 +4492,7 @@
         <v>8.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -4500,7 +4500,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -4524,7 +4524,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -4532,7 +4532,7 @@
         <v>158.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         <v>174.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -4564,7 +4564,7 @@
         <v>292.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -4572,7 +4572,7 @@
         <v>308.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -4580,7 +4580,7 @@
         <v>324.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -4604,7 +4604,7 @@
         <v>442.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4612,7 +4612,7 @@
         <v>458.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -4620,7 +4620,7 @@
         <v>474.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -4644,7 +4644,7 @@
         <v>592.5</v>
       </c>
       <c r="B24" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
@@ -4652,7 +4652,7 @@
         <v>608.5</v>
       </c>
       <c r="B25" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -4660,7 +4660,7 @@
         <v>624.5</v>
       </c>
       <c r="B26" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -4684,7 +4684,7 @@
         <v>742.5</v>
       </c>
       <c r="B29" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
@@ -4692,7 +4692,7 @@
         <v>758.5</v>
       </c>
       <c r="B30" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -4700,7 +4700,7 @@
         <v>774.5</v>
       </c>
       <c r="B31" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -4724,7 +4724,7 @@
         <v>892.5</v>
       </c>
       <c r="B34" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="35">
@@ -4732,7 +4732,7 @@
         <v>908.5</v>
       </c>
       <c r="B35" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="36">
@@ -4740,7 +4740,7 @@
         <v>924.5</v>
       </c>
       <c r="B36" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="37">
@@ -4764,7 +4764,7 @@
         <v>1042.5</v>
       </c>
       <c r="B39" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="40">
@@ -4772,7 +4772,7 @@
         <v>1058.5</v>
       </c>
       <c r="B40" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="41">
@@ -4780,7 +4780,7 @@
         <v>1074.5</v>
       </c>
       <c r="B41" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="42">
@@ -4846,7 +4846,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -4854,7 +4854,7 @@
         <v>8.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -4862,7 +4862,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -4886,7 +4886,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -4894,7 +4894,7 @@
         <v>158.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -4902,7 +4902,7 @@
         <v>174.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -4926,7 +4926,7 @@
         <v>292.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -4934,7 +4934,7 @@
         <v>308.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
         <v>324.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -4966,7 +4966,7 @@
         <v>442.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -4974,7 +4974,7 @@
         <v>458.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -4982,7 +4982,7 @@
         <v>474.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -5006,7 +5006,7 @@
         <v>592.5</v>
       </c>
       <c r="B24" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
@@ -5014,7 +5014,7 @@
         <v>608.5</v>
       </c>
       <c r="B25" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -5022,7 +5022,7 @@
         <v>624.5</v>
       </c>
       <c r="B26" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -5046,7 +5046,7 @@
         <v>742.5</v>
       </c>
       <c r="B29" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
@@ -5054,7 +5054,7 @@
         <v>758.5</v>
       </c>
       <c r="B30" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -5062,7 +5062,7 @@
         <v>774.5</v>
       </c>
       <c r="B31" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -5086,7 +5086,7 @@
         <v>892.5</v>
       </c>
       <c r="B34" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="35">
@@ -5094,7 +5094,7 @@
         <v>908.5</v>
       </c>
       <c r="B35" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="36">
@@ -5102,7 +5102,7 @@
         <v>924.5</v>
       </c>
       <c r="B36" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="37">
@@ -5126,7 +5126,7 @@
         <v>1042.5</v>
       </c>
       <c r="B39" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="40">
@@ -5134,7 +5134,7 @@
         <v>1058.5</v>
       </c>
       <c r="B40" t="n">
-        <v>-100</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="41">
@@ -5142,7 +5142,7 @@
         <v>1074.5</v>
       </c>
       <c r="B41" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="42">
@@ -5208,15 +5208,15 @@
         <v>-13</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>-5.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -5224,7 +5224,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -5248,15 +5248,15 @@
         <v>487</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>511</v>
+        <v>494.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -5264,7 +5264,7 @@
         <v>502</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -5396,15 +5396,15 @@
         <v>-13.5</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="B5" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="6">
@@ -5412,7 +5412,7 @@
         <v>1.5</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -5436,15 +5436,15 @@
         <v>137.5</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B10" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="11">
@@ -5452,7 +5452,7 @@
         <v>152.5</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -5476,15 +5476,15 @@
         <v>287.5</v>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B15" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="16">
@@ -5492,7 +5492,7 @@
         <v>302.5</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -5516,15 +5516,15 @@
         <v>437.5</v>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B20" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="21">
@@ -5532,7 +5532,7 @@
         <v>452.5</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -5598,15 +5598,15 @@
         <v>-13.5</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="B5" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="6">
@@ -5614,7 +5614,7 @@
         <v>1.5</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -5638,15 +5638,15 @@
         <v>137.5</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B10" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="11">
@@ -5654,7 +5654,7 @@
         <v>152.5</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -5678,15 +5678,15 @@
         <v>287.5</v>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B15" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="16">
@@ -5694,7 +5694,7 @@
         <v>302.5</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -5718,15 +5718,15 @@
         <v>437.5</v>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B20" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="21">
@@ -5734,7 +5734,7 @@
         <v>452.5</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -5800,7 +5800,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -5808,7 +5808,7 @@
         <v>11.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="6">
@@ -5816,7 +5816,7 @@
         <v>30.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -5840,7 +5840,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -5848,7 +5848,7 @@
         <v>161.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="11">
@@ -5856,7 +5856,7 @@
         <v>180.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5996,7 +5996,7 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -6004,7 +6004,7 @@
         <v>-5.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="6">
@@ -6012,7 +6012,7 @@
         <v>24.5</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -6036,7 +6036,7 @@
         <v>114.5</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -6044,7 +6044,7 @@
         <v>144.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="11">
@@ -6052,7 +6052,7 @@
         <v>174.5</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -6076,7 +6076,7 @@
         <v>264.5</v>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -6084,7 +6084,7 @@
         <v>294.5</v>
       </c>
       <c r="B15" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="16">
@@ -6092,7 +6092,7 @@
         <v>324.5</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -6116,7 +6116,7 @@
         <v>414.5</v>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -6124,7 +6124,7 @@
         <v>444.5</v>
       </c>
       <c r="B20" t="n">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="21">
@@ -6132,7 +6132,7 @@
         <v>474.5</v>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -6198,7 +6198,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -6206,7 +6206,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="6">
@@ -6214,7 +6214,7 @@
         <v>45.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -6238,7 +6238,7 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -6246,7 +6246,7 @@
         <v>169</v>
       </c>
       <c r="B10" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="11">
@@ -6254,7 +6254,7 @@
         <v>195.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -6278,7 +6278,7 @@
         <v>292.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -6286,7 +6286,7 @@
         <v>319</v>
       </c>
       <c r="B15" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>345.5</v>
       </c>
       <c r="B16" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -6318,7 +6318,7 @@
         <v>442.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -6326,7 +6326,7 @@
         <v>469</v>
       </c>
       <c r="B20" t="n">
-        <v>-125</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="21">
@@ -6334,7 +6334,7 @@
         <v>495.5</v>
       </c>
       <c r="B21" t="n">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -6400,15 +6400,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -6416,7 +6416,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -6440,15 +6440,15 @@
         <v>492.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -6456,7 +6456,7 @@
         <v>507.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -6522,15 +6522,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -6538,7 +6538,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -6562,15 +6562,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -6578,7 +6578,7 @@
         <v>157.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -6602,15 +6602,15 @@
         <v>292.5</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="B15" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="16">
@@ -6618,7 +6618,7 @@
         <v>307.5</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -6642,15 +6642,15 @@
         <v>442.5</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B20" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="21">
@@ -6658,7 +6658,7 @@
         <v>457.5</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -6682,15 +6682,15 @@
         <v>592.5</v>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="B25" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="26">
@@ -6698,7 +6698,7 @@
         <v>607.5</v>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -6722,15 +6722,15 @@
         <v>742.5</v>
       </c>
       <c r="B29" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="B30" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="31">
@@ -6738,7 +6738,7 @@
         <v>757.5</v>
       </c>
       <c r="B31" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -6762,15 +6762,15 @@
         <v>892.5</v>
       </c>
       <c r="B34" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="B35" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="36">
@@ -6778,7 +6778,7 @@
         <v>907.5</v>
       </c>
       <c r="B36" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="37">
@@ -6802,15 +6802,15 @@
         <v>1042.5</v>
       </c>
       <c r="B39" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="B40" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="41">
@@ -6818,7 +6818,7 @@
         <v>1057.5</v>
       </c>
       <c r="B41" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="42">
@@ -6884,15 +6884,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -6900,7 +6900,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -6924,15 +6924,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -6940,7 +6940,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -7006,15 +7006,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -7022,7 +7022,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -7046,15 +7046,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -7062,7 +7062,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -7128,15 +7128,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -7144,7 +7144,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -7168,15 +7168,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -7184,7 +7184,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -7208,15 +7208,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -7224,7 +7224,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -7488,15 +7488,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -7504,7 +7504,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -7528,15 +7528,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -7544,7 +7544,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -7882,15 +7882,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -7898,7 +7898,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -7922,15 +7922,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -7938,7 +7938,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8004,15 +8004,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -8020,7 +8020,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8044,15 +8044,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -8060,7 +8060,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8126,15 +8126,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -8142,7 +8142,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8166,15 +8166,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -8182,7 +8182,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8248,15 +8248,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -8264,7 +8264,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8288,15 +8288,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -8304,7 +8304,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8328,15 +8328,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -8344,7 +8344,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -8368,15 +8368,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -8384,7 +8384,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -8450,15 +8450,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -8466,7 +8466,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8490,15 +8490,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -8506,7 +8506,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8530,15 +8530,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -8546,7 +8546,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -8570,15 +8570,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -8586,7 +8586,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -8652,15 +8652,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -8668,7 +8668,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8692,15 +8692,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -8708,7 +8708,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -8732,15 +8732,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -8748,7 +8748,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -8772,15 +8772,15 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>595</v>
+        <v>608.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -8788,7 +8788,7 @@
         <v>624</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -8812,15 +8812,15 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>795</v>
+        <v>808.25</v>
       </c>
       <c r="B25" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -8828,7 +8828,7 @@
         <v>824</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -8852,15 +8852,15 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>995</v>
+        <v>1008.25</v>
       </c>
       <c r="B30" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -8868,7 +8868,7 @@
         <v>1024</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -8934,15 +8934,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -8950,7 +8950,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -8974,15 +8974,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -8990,7 +8990,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -9056,15 +9056,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="6">
@@ -9072,7 +9072,7 @@
         <v>34.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -9096,15 +9096,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>272</v>
+        <v>263.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="11">
@@ -9112,7 +9112,7 @@
         <v>284.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -9178,15 +9178,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="6">
@@ -9194,7 +9194,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="7">
@@ -9218,15 +9218,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>167.5</v>
+        <v>168.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="11">
@@ -9234,7 +9234,7 @@
         <v>194.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="12">
@@ -9300,15 +9300,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -9316,7 +9316,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -9340,15 +9340,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -9356,7 +9356,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -9554,15 +9554,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -9570,7 +9570,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -9594,15 +9594,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -9610,7 +9610,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -9676,7 +9676,7 @@
         <v>-35</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -9684,7 +9684,7 @@
         <v>-10</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -9692,7 +9692,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -9716,7 +9716,7 @@
         <v>215</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -9724,7 +9724,7 @@
         <v>240</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -9732,7 +9732,7 @@
         <v>265</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -9798,15 +9798,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -9814,7 +9814,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -9838,15 +9838,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -9854,7 +9854,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -10052,15 +10052,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -10068,7 +10068,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -10092,15 +10092,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -10108,7 +10108,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -10406,15 +10406,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -10422,7 +10422,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -10446,15 +10446,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -10462,7 +10462,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -10486,15 +10486,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -10502,7 +10502,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -10526,15 +10526,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -10542,7 +10542,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -10608,15 +10608,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -10624,7 +10624,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -10648,15 +10648,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -10664,7 +10664,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -10688,15 +10688,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -10704,7 +10704,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -10728,15 +10728,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -10744,7 +10744,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -11106,15 +11106,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -11122,7 +11122,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -11146,15 +11146,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -11162,7 +11162,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -11186,15 +11186,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -11202,7 +11202,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -11226,15 +11226,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -11242,7 +11242,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -11374,15 +11374,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -11390,7 +11390,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -11414,15 +11414,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -11430,7 +11430,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -11454,15 +11454,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -11470,7 +11470,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -11494,15 +11494,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -11510,7 +11510,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -11576,15 +11576,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -11592,7 +11592,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -11616,15 +11616,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -11632,7 +11632,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -11656,15 +11656,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -11672,7 +11672,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -11696,15 +11696,15 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>595</v>
+        <v>608.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -11712,7 +11712,7 @@
         <v>624</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -11736,15 +11736,15 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>795</v>
+        <v>808.25</v>
       </c>
       <c r="B25" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -11752,7 +11752,7 @@
         <v>824</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -11776,15 +11776,15 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>995</v>
+        <v>1008.25</v>
       </c>
       <c r="B30" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -11792,7 +11792,7 @@
         <v>1024</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -11940,15 +11940,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="6">
@@ -11956,7 +11956,7 @@
         <v>34.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -11980,15 +11980,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>272</v>
+        <v>263.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="11">
@@ -11996,7 +11996,7 @@
         <v>284.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -12062,15 +12062,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="6">
@@ -12078,7 +12078,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="7">
@@ -12102,15 +12102,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>167.5</v>
+        <v>168.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="11">
@@ -12118,7 +12118,7 @@
         <v>194.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="12">
@@ -12184,15 +12184,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -12200,7 +12200,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -12224,15 +12224,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -12240,7 +12240,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -12438,15 +12438,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -12454,7 +12454,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -12478,15 +12478,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -12494,7 +12494,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -12560,7 +12560,7 @@
         <v>-35</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -12568,7 +12568,7 @@
         <v>-10</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -12576,7 +12576,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -12600,7 +12600,7 @@
         <v>215</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -12608,7 +12608,7 @@
         <v>240</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -12616,7 +12616,7 @@
         <v>265</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -12682,15 +12682,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -12698,7 +12698,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -12722,15 +12722,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -12738,7 +12738,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -13234,15 +13234,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -13250,7 +13250,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -13274,15 +13274,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -13290,7 +13290,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -13314,15 +13314,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -13330,7 +13330,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -13354,15 +13354,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -13370,7 +13370,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -13436,15 +13436,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -13452,7 +13452,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -13476,15 +13476,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -13492,7 +13492,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -13516,15 +13516,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -13532,7 +13532,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -13556,15 +13556,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -13572,7 +13572,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -13638,15 +13638,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -13654,7 +13654,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -13678,15 +13678,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -13694,7 +13694,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -13718,15 +13718,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -13734,7 +13734,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -13758,15 +13758,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -13774,7 +13774,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -13840,15 +13840,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -13856,7 +13856,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -13880,15 +13880,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -13896,7 +13896,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -13920,15 +13920,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -13936,7 +13936,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -13960,15 +13960,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -13976,7 +13976,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -14042,15 +14042,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -14058,7 +14058,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -14082,15 +14082,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -14098,7 +14098,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -14122,15 +14122,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -14138,7 +14138,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -14162,15 +14162,15 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>595</v>
+        <v>608.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -14178,7 +14178,7 @@
         <v>624</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -14202,15 +14202,15 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>795</v>
+        <v>808.25</v>
       </c>
       <c r="B25" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -14218,7 +14218,7 @@
         <v>824</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -14242,15 +14242,15 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>995</v>
+        <v>1008.25</v>
       </c>
       <c r="B30" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -14258,7 +14258,7 @@
         <v>1024</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -14324,15 +14324,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="6">
@@ -14340,7 +14340,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="7">
@@ -14364,15 +14364,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>167.5</v>
+        <v>168.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="11">
@@ -14380,7 +14380,7 @@
         <v>194.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="12">
@@ -14512,15 +14512,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -14528,7 +14528,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -14552,15 +14552,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -14568,7 +14568,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -14766,15 +14766,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -14782,7 +14782,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -14806,15 +14806,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -14822,7 +14822,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -14888,7 +14888,7 @@
         <v>-35</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -14896,7 +14896,7 @@
         <v>-10</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -14904,7 +14904,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -14928,7 +14928,7 @@
         <v>215</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -14936,7 +14936,7 @@
         <v>240</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -14944,7 +14944,7 @@
         <v>265</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -15010,15 +15010,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -15026,7 +15026,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -15050,15 +15050,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -15066,7 +15066,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -15380,15 +15380,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -15396,7 +15396,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -15420,15 +15420,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -15436,7 +15436,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -15618,15 +15618,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -15634,7 +15634,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -15658,15 +15658,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -15674,7 +15674,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -15698,15 +15698,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -15714,7 +15714,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -15738,15 +15738,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -15754,7 +15754,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -15820,15 +15820,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -15836,7 +15836,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -15860,15 +15860,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -15876,7 +15876,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -15900,15 +15900,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -15916,7 +15916,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -15940,15 +15940,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -15956,7 +15956,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -16022,15 +16022,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -16038,7 +16038,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16062,15 +16062,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -16078,7 +16078,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16144,15 +16144,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -16160,7 +16160,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16184,15 +16184,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -16200,7 +16200,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16266,15 +16266,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -16282,7 +16282,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16306,15 +16306,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -16322,7 +16322,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16346,15 +16346,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -16362,7 +16362,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -16626,15 +16626,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -16642,7 +16642,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16666,15 +16666,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -16682,7 +16682,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16748,15 +16748,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -16764,7 +16764,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16788,15 +16788,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -16804,7 +16804,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16870,15 +16870,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -16886,7 +16886,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -16910,15 +16910,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -16926,7 +16926,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -16992,15 +16992,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -17008,7 +17008,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -17032,15 +17032,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -17048,7 +17048,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -17072,15 +17072,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -17088,7 +17088,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -17112,15 +17112,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -17128,7 +17128,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -17194,15 +17194,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -17210,7 +17210,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -17234,15 +17234,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -17250,7 +17250,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -17274,15 +17274,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -17290,7 +17290,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -17314,15 +17314,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -17330,7 +17330,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -17396,15 +17396,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -17412,7 +17412,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -17436,15 +17436,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -17452,7 +17452,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -17476,15 +17476,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -17492,7 +17492,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -17516,15 +17516,15 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>595</v>
+        <v>608.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -17532,7 +17532,7 @@
         <v>624</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -17556,15 +17556,15 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>795</v>
+        <v>808.25</v>
       </c>
       <c r="B25" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -17572,7 +17572,7 @@
         <v>824</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -17596,15 +17596,15 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>995</v>
+        <v>1008.25</v>
       </c>
       <c r="B30" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -17612,7 +17612,7 @@
         <v>1024</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -17678,15 +17678,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="6">
@@ -17694,7 +17694,7 @@
         <v>34.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -17718,15 +17718,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>272</v>
+        <v>263.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="11">
@@ -17734,7 +17734,7 @@
         <v>284.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -17800,15 +17800,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="6">
@@ -17816,7 +17816,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="7">
@@ -17840,15 +17840,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>167.5</v>
+        <v>168.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="11">
@@ -17856,7 +17856,7 @@
         <v>194.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="12">
@@ -17922,15 +17922,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -17938,7 +17938,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -17962,15 +17962,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -17978,7 +17978,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -18176,15 +18176,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -18192,7 +18192,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -18216,15 +18216,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -18232,7 +18232,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -18256,15 +18256,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -18272,7 +18272,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -18338,15 +18338,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -18354,7 +18354,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -18378,15 +18378,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -18394,7 +18394,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -18460,7 +18460,7 @@
         <v>-35</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -18468,7 +18468,7 @@
         <v>-10</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -18476,7 +18476,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -18500,7 +18500,7 @@
         <v>215</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -18508,7 +18508,7 @@
         <v>240</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -18516,7 +18516,7 @@
         <v>265</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -18582,15 +18582,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -18598,7 +18598,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -18622,15 +18622,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -18638,7 +18638,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -19068,15 +19068,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -19084,7 +19084,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -19108,15 +19108,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -19124,7 +19124,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -19148,15 +19148,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -19164,7 +19164,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -19188,15 +19188,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -19204,7 +19204,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -19336,15 +19336,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -19352,7 +19352,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -19376,15 +19376,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -19392,7 +19392,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -19416,15 +19416,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -19432,7 +19432,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -19456,15 +19456,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -19472,7 +19472,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -19538,15 +19538,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -19554,7 +19554,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -19578,15 +19578,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -19594,7 +19594,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -19618,15 +19618,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -19634,7 +19634,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -19658,15 +19658,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -19674,7 +19674,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -19740,15 +19740,15 @@
         <v>-35.5</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="B5" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -19756,7 +19756,7 @@
         <v>27.5</v>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -19780,15 +19780,15 @@
         <v>214.5</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B10" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -19796,7 +19796,7 @@
         <v>277.5</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -19820,15 +19820,15 @@
         <v>464.5</v>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -19836,7 +19836,7 @@
         <v>527.5</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -19860,15 +19860,15 @@
         <v>714.5</v>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B20" t="n">
-        <v>-22</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -19876,7 +19876,7 @@
         <v>777.5</v>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -19942,15 +19942,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-5</v>
+        <v>8.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="6">
@@ -19958,7 +19958,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -19982,15 +19982,15 @@
         <v>192.5</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>195</v>
+        <v>208.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="11">
@@ -19998,7 +19998,7 @@
         <v>224</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -20022,15 +20022,15 @@
         <v>392.5</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>395</v>
+        <v>408.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="16">
@@ -20038,7 +20038,7 @@
         <v>424</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -20062,15 +20062,15 @@
         <v>592.5</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>595</v>
+        <v>608.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="21">
@@ -20078,7 +20078,7 @@
         <v>624</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -20102,15 +20102,15 @@
         <v>792.5</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>795</v>
+        <v>808.25</v>
       </c>
       <c r="B25" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="26">
@@ -20118,7 +20118,7 @@
         <v>824</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="27">
@@ -20142,15 +20142,15 @@
         <v>992.5</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>995</v>
+        <v>1008.25</v>
       </c>
       <c r="B30" t="n">
-        <v>-50</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="31">
@@ -20158,7 +20158,7 @@
         <v>1024</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="32">
@@ -20224,15 +20224,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="6">
@@ -20240,7 +20240,7 @@
         <v>44.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="7">
@@ -20264,15 +20264,15 @@
         <v>142.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>167.5</v>
+        <v>168.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-53</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="11">
@@ -20280,7 +20280,7 @@
         <v>194.5</v>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="12">
@@ -20346,15 +20346,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="6">
@@ -20362,7 +20362,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -20386,15 +20386,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B10" t="n">
-        <v>-28</v>
+        <v>-35.5</v>
       </c>
     </row>
     <row r="11">
@@ -20402,7 +20402,7 @@
         <v>257.5</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -20600,15 +20600,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -20616,7 +20616,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -20640,15 +20640,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -20656,7 +20656,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -20722,7 +20722,7 @@
         <v>-35</v>
       </c>
       <c r="B4" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -20730,7 +20730,7 @@
         <v>-10</v>
       </c>
       <c r="B5" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="6">
@@ -20738,7 +20738,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -20762,7 +20762,7 @@
         <v>215</v>
       </c>
       <c r="B9" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -20770,7 +20770,7 @@
         <v>240</v>
       </c>
       <c r="B10" t="n">
-        <v>-65</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="11">
@@ -20778,7 +20778,7 @@
         <v>265</v>
       </c>
       <c r="B11" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -20910,15 +20910,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="6">
@@ -20926,7 +20926,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -20950,15 +20950,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>268</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-100</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="11">
@@ -20966,7 +20966,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -21396,15 +21396,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -21412,7 +21412,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -21436,15 +21436,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -21452,7 +21452,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -21476,15 +21476,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -21492,7 +21492,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -21516,15 +21516,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -21532,7 +21532,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -21598,15 +21598,15 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -21614,7 +21614,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -21638,15 +21638,15 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>285</v>
+        <v>261.25</v>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -21654,7 +21654,7 @@
         <v>280</v>
       </c>
       <c r="B11" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -21678,15 +21678,15 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>535</v>
+        <v>511.25</v>
       </c>
       <c r="B15" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -21694,7 +21694,7 @@
         <v>530</v>
       </c>
       <c r="B16" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -21718,15 +21718,15 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>785</v>
+        <v>761.25</v>
       </c>
       <c r="B20" t="n">
-        <v>-70</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -21734,7 +21734,7 @@
         <v>780</v>
       </c>
       <c r="B21" t="n">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">
@@ -21800,7 +21800,7 @@
         <v>-7.5</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="5">
@@ -21808,7 +21808,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="6">
@@ -21816,7 +21816,7 @@
         <v>77.5</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7">
@@ -21840,7 +21840,7 @@
         <v>242.5</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="10">
@@ -21848,7 +21848,7 @@
         <v>285</v>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="11">
@@ -21856,7 +21856,7 @@
         <v>327.5</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="12">
@@ -21880,7 +21880,7 @@
         <v>492.5</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="15">
@@ -21888,7 +21888,7 @@
         <v>535</v>
       </c>
       <c r="B15" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="16">
@@ -21896,7 +21896,7 @@
         <v>577.5</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="17">
@@ -21920,7 +21920,7 @@
         <v>742.5</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20">
@@ -21928,7 +21928,7 @@
         <v>785</v>
       </c>
       <c r="B20" t="n">
-        <v>-24</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="21">
@@ -21936,7 +21936,7 @@
         <v>827.5</v>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="22">

--- a/probe_contours.xlsx
+++ b/probe_contours.xlsx
@@ -2281,7 +2281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,7 +2328,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -2347,12 +2347,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2367,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,7 +2436,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -2422,10 +2444,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -2433,12 +2455,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -11727,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,7 +11818,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -11782,10 +11826,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -11793,12 +11837,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11813,7 +11879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11860,7 +11926,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -11868,10 +11934,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -11879,12 +11945,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -11899,7 +11987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11946,7 +12034,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -11954,10 +12042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -11965,12 +12053,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11985,7 +12095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12032,7 +12142,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -12040,10 +12150,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -12051,12 +12161,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -14921,7 +15053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14968,7 +15100,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -14976,10 +15108,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -14987,12 +15119,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -15007,7 +15161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15054,7 +15208,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -15062,10 +15216,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -15073,12 +15227,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -15093,7 +15269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15140,7 +15316,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -15148,10 +15324,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -15159,12 +15335,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -15179,7 +15377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15226,7 +15424,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -15234,10 +15432,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -15245,12 +15443,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -17471,7 +17691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17518,7 +17738,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -17526,10 +17746,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -17537,12 +17757,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17557,7 +17799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17604,7 +17846,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -17612,10 +17854,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -17623,12 +17865,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -17805,7 +18069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17852,7 +18116,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -17860,10 +18124,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -17871,12 +18135,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17891,7 +18177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17938,7 +18224,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -17946,10 +18232,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -17957,12 +18243,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21491,7 +21799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21538,7 +21846,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -21546,10 +21854,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -21557,12 +21865,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21577,7 +21907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21624,7 +21954,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -21632,10 +21962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -21643,12 +21973,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21663,7 +22015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21710,7 +22062,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -21718,10 +22070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -21729,12 +22081,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21749,7 +22123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21796,7 +22170,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -21804,10 +22178,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -21815,12 +22189,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -24107,7 +24503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24154,7 +24550,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -24162,10 +24558,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -24173,12 +24569,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -24193,7 +24611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24240,7 +24658,7 @@
         <v>-62</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -24248,10 +24666,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78</v>
+        <v>-62</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -24259,12 +24677,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>78</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -24279,7 +24719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24326,7 +24766,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>15</v>
@@ -24334,10 +24774,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>15</v>
@@ -24345,12 +24785,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -24365,7 +24827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24412,7 +24874,7 @@
         <v>-70</v>
       </c>
       <c r="B4" t="n">
-        <v>-56</v>
+        <v>-11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
@@ -24420,10 +24882,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70</v>
+        <v>-70</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>-156</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
@@ -24431,12 +24893,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>70</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="n">
         <v>30000</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
         <v>30</v>
       </c>
     </row>

--- a/probe_contours.xlsx
+++ b/probe_contours.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,11 +609,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -622,9 +617,6 @@
       <c r="B2" t="n">
         <v>6000</v>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -633,9 +625,6 @@
       <c r="B3" t="n">
         <v>257.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -644,9 +633,6 @@
       <c r="B4" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -655,9 +641,6 @@
       <c r="B5" t="n">
         <v>-77.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -666,9 +649,6 @@
       <c r="B6" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -677,9 +657,6 @@
       <c r="B7" t="n">
         <v>257.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -687,9 +664,6 @@
       </c>
       <c r="B8" t="n">
         <v>6000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2281,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2295,11 +2269,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2308,9 +2277,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2319,9 +2285,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2330,9 +2293,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2341,9 +2301,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2352,9 +2309,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2363,9 +2317,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2373,9 +2324,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2389,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,11 +2351,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2416,9 +2359,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2427,9 +2367,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2438,9 +2375,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2449,9 +2383,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2460,9 +2391,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2471,9 +2399,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2481,9 +2406,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -6006,7 +5928,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-14.5</v>
+        <v>-16</v>
       </c>
       <c r="B40" t="n">
         <v>600</v>
@@ -6014,7 +5936,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="B41" t="n">
         <v>400</v>
@@ -6022,7 +5944,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-11.5</v>
+        <v>-16</v>
       </c>
       <c r="B42" t="n">
         <v>200</v>
@@ -6030,7 +5952,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -6062,7 +5984,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -6070,7 +5992,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="B48" t="n">
         <v>200</v>
@@ -6078,7 +6000,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B49" t="n">
         <v>400</v>
@@ -6086,7 +6008,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="B50" t="n">
         <v>600</v>
@@ -11771,7 +11693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11785,11 +11707,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -11798,9 +11715,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -11809,9 +11723,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11820,9 +11731,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -11831,9 +11739,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -11842,9 +11747,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -11853,9 +11755,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -11863,9 +11762,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -11879,7 +11775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11893,11 +11789,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -11906,9 +11797,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -11917,9 +11805,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11928,9 +11813,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -11939,9 +11821,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -11950,9 +11829,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -11961,9 +11837,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -11971,9 +11844,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -11987,7 +11857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12001,11 +11871,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -12014,9 +11879,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12025,9 +11887,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12036,9 +11895,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -12047,9 +11903,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -12058,9 +11911,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -12069,9 +11919,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -12079,9 +11926,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -12095,7 +11939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12109,11 +11953,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -12122,9 +11961,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12133,9 +11969,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12144,9 +11977,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -12155,9 +11985,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -12166,9 +11993,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -12177,9 +12001,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -12187,9 +12008,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -12607,7 +12425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12621,11 +12439,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -12634,9 +12447,6 @@
       <c r="B2" t="n">
         <v>6000</v>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12645,9 +12455,6 @@
       <c r="B3" t="n">
         <v>257.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12656,9 +12463,6 @@
       <c r="B4" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -12667,9 +12471,6 @@
       <c r="B5" t="n">
         <v>-77.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -12678,9 +12479,6 @@
       <c r="B6" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -12689,9 +12487,6 @@
       <c r="B7" t="n">
         <v>257.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -12699,9 +12494,6 @@
       </c>
       <c r="B8" t="n">
         <v>6000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12715,7 +12507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12729,11 +12521,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -12742,9 +12529,6 @@
       <c r="B2" t="n">
         <v>9000</v>
       </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -12753,9 +12537,6 @@
       <c r="B3" t="n">
         <v>257.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12764,9 +12545,6 @@
       <c r="B4" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -12775,9 +12553,6 @@
       <c r="B5" t="n">
         <v>-77.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -12786,9 +12561,6 @@
       <c r="B6" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -12797,9 +12569,6 @@
       <c r="B7" t="n">
         <v>257.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -12807,9 +12576,6 @@
       </c>
       <c r="B8" t="n">
         <v>9000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -13883,7 +13649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13897,11 +13663,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -13910,9 +13671,6 @@
       <c r="B2" t="n">
         <v>9000</v>
       </c>
-      <c r="C2" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -13921,9 +13679,6 @@
       <c r="B3" t="n">
         <v>257.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13932,9 +13687,6 @@
       <c r="B4" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -13943,9 +13695,6 @@
       <c r="B5" t="n">
         <v>-77.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -13954,9 +13703,6 @@
       <c r="B6" t="n">
         <v>-7.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -13965,9 +13711,6 @@
       <c r="B7" t="n">
         <v>257.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13975,9 +13718,6 @@
       </c>
       <c r="B8" t="n">
         <v>9000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15053,7 +14793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15067,11 +14807,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -15080,9 +14815,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15091,9 +14823,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15102,9 +14831,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15113,9 +14839,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15124,9 +14847,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15135,9 +14855,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15145,9 +14862,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15161,7 +14875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15175,11 +14889,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -15188,9 +14897,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15199,9 +14905,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15210,9 +14913,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15221,9 +14921,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15232,9 +14929,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15243,9 +14937,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15253,9 +14944,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -15269,7 +14957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15283,11 +14971,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -15296,9 +14979,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15307,9 +14987,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15318,9 +14995,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15329,9 +15003,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15340,9 +15011,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15351,9 +15019,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15361,9 +15026,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15377,7 +15039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15391,11 +15053,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -15404,9 +15061,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -15415,9 +15069,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15426,9 +15077,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -15437,9 +15085,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15448,9 +15093,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15459,9 +15101,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15469,9 +15108,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -17691,7 +17327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17705,11 +17341,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -17718,9 +17349,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -17729,9 +17357,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -17740,9 +17365,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -17751,9 +17373,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -17762,9 +17381,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -17773,9 +17389,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -17783,9 +17396,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -17799,7 +17409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17813,11 +17423,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -17826,9 +17431,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -17837,9 +17439,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -17848,9 +17447,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -17859,9 +17455,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -17870,9 +17463,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -17881,9 +17471,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -17891,9 +17478,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -18069,7 +17653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18083,11 +17667,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -18096,9 +17675,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -18107,9 +17683,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18118,9 +17691,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -18129,9 +17699,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -18140,9 +17707,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -18151,9 +17715,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -18161,9 +17722,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -18177,7 +17735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18191,11 +17749,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -18204,9 +17757,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -18215,9 +17765,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18226,9 +17773,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -18237,9 +17781,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -18248,9 +17789,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -18259,9 +17797,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -18269,9 +17804,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -21799,7 +21331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21813,11 +21345,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21826,9 +21353,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -21837,9 +21361,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21848,9 +21369,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -21859,9 +21377,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21870,9 +21385,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -21881,9 +21393,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21891,9 +21400,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -21907,7 +21413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21921,11 +21427,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -21934,9 +21435,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -21945,9 +21443,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21956,9 +21451,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -21967,9 +21459,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21978,9 +21467,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -21989,9 +21475,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21999,9 +21482,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -22015,7 +21495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22029,11 +21509,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -22042,9 +21517,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -22053,9 +21525,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -22064,9 +21533,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -22075,9 +21541,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -22086,9 +21549,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -22097,9 +21557,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -22107,9 +21564,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -22123,7 +21577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22137,11 +21591,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -22150,9 +21599,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -22161,9 +21607,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -22172,9 +21615,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -22183,9 +21623,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -22194,9 +21631,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -22205,9 +21639,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -22215,9 +21646,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -24503,7 +23931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24517,11 +23945,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -24530,9 +23953,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -24541,9 +23961,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -24552,9 +23969,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -24563,9 +23977,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -24574,9 +23985,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -24585,9 +23993,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -24595,9 +24000,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -24611,7 +24013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24625,11 +24027,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -24638,9 +24035,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -24649,9 +24043,6 @@
       <c r="B3" t="n">
         <v>34</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -24660,9 +24051,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -24671,9 +24059,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -24682,9 +24067,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -24693,9 +24075,6 @@
       <c r="B7" t="n">
         <v>34</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -24703,9 +24082,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -24719,7 +24095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24733,11 +24109,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -24746,9 +24117,6 @@
       <c r="B2" t="n">
         <v>15000</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -24757,9 +24125,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -24768,9 +24133,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -24779,9 +24141,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -24790,9 +24149,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -24801,9 +24157,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -24811,9 +24164,6 @@
       </c>
       <c r="B8" t="n">
         <v>15000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -24827,7 +24177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24841,11 +24191,6 @@
           <t>y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>shank_length_mm</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -24854,9 +24199,6 @@
       <c r="B2" t="n">
         <v>30000</v>
       </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -24865,9 +24207,6 @@
       <c r="B3" t="n">
         <v>118</v>
       </c>
-      <c r="C3" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -24876,9 +24215,6 @@
       <c r="B4" t="n">
         <v>-11</v>
       </c>
-      <c r="C4" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -24887,9 +24223,6 @@
       <c r="B5" t="n">
         <v>-156</v>
       </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -24898,9 +24231,6 @@
       <c r="B6" t="n">
         <v>-11</v>
       </c>
-      <c r="C6" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -24909,9 +24239,6 @@
       <c r="B7" t="n">
         <v>118</v>
       </c>
-      <c r="C7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -24919,9 +24246,6 @@
       </c>
       <c r="B8" t="n">
         <v>30000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
